--- a/verificables revisión sistemática/S23_clase_de_resistencia_comprobada.xlsx
+++ b/verificables revisión sistemática/S23_clase_de_resistencia_comprobada.xlsx
@@ -701,7 +701,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-03</t>
+          <t>Generado el 2026-10-06</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S23_clase_de_resistencia_comprobada.xlsx
+++ b/verificables revisión sistemática/S23_clase_de_resistencia_comprobada.xlsx
@@ -701,7 +701,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-06</t>
+          <t>Generado el 2026-10-07</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S23_clase_de_resistencia_comprobada.xlsx
+++ b/verificables revisión sistemática/S23_clase_de_resistencia_comprobada.xlsx
@@ -701,7 +701,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-07</t>
+          <t>Generado el 2026-10-08</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S23_clase_de_resistencia_comprobada.xlsx
+++ b/verificables revisión sistemática/S23_clase_de_resistencia_comprobada.xlsx
@@ -701,7 +701,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-08</t>
+          <t>Generado el 2026-10-12</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S23_clase_de_resistencia_comprobada.xlsx
+++ b/verificables revisión sistemática/S23_clase_de_resistencia_comprobada.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +41,10 @@
       <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -89,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -100,11 +104,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -472,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -521,187 +528,194 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Las secciones y tablas que se citan son las del informe extendido (manuscrito maestro). En el manuscrito preparado para la revista las secciones no van numeradas.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Cuántas filas</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>70 filas de datos</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Qué significa cada columna</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Estudio</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>columna interna: study_id</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>clase_en_la_extraccion_antes</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>columna interna: clase_en_la_extraccion_antes</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>procedencia_antes</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>columna interna: procedencia_antes</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>verificacion</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>columna interna: verificacion</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>clase_verificada_codificada</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>columna interna: clase_verificada_codificada</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>relacion_con_la_declarada</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>columna interna: relacion_con_la_declarada</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>cambia_en_la_extraccion</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>columna interna: cambia_en_la_extraccion</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>queda_abierto</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>columna interna: queda_abierto</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>clase_verificada_firmada</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>columna interna: clase_verificada_firmada</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>criterio_o_antibiograma_firmado</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>columna interna: criterio_o_antibiograma_firmado</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>firmado_por</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>columna interna: firmado_por</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>columna interna: fecha</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>El CSV con los nombres internos acompaña a este fichero: es la copia reproducible.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>Generado el 2026-10-12</t>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Generado el 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -734,62 +748,62 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Estudio</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>clase_en_la_extraccion_antes</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>procedencia_antes</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>verificacion</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>clase_verificada_codificada</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>relacion_con_la_declarada</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>cambia_en_la_extraccion</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>queda_abierto</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>clase_verificada_firmada</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>criterio_o_antibiograma_firmado</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>firmado_por</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>

--- a/verificables revisión sistemática/S23_clase_de_resistencia_comprobada.xlsx
+++ b/verificables revisión sistemática/S23_clase_de_resistencia_comprobada.xlsx
@@ -715,7 +715,7 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-14</t>
+          <t>Generado el 2026-10-15</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S23_clase_de_resistencia_comprobada.xlsx
+++ b/verificables revisión sistemática/S23_clase_de_resistencia_comprobada.xlsx
@@ -715,7 +715,7 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-15</t>
+          <t>Generado el 2026-10-19</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S23_clase_de_resistencia_comprobada.xlsx
+++ b/verificables revisión sistemática/S23_clase_de_resistencia_comprobada.xlsx
@@ -506,7 +506,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>La clase de resistencia de cada estudio con texto completo, comprobada contra el antibiograma del artículo, con la conclusión firmada por los dos autores.</t>
+          <t>La clase de resistencia de cada estudio con texto completo, comprobada contra el antibiograma del artículo, con la conclusión firmada por los dos autores en la relectura del 30 de septiembre de 2026. Lo firmado es el texto libre de «Clase verificada (texto firmado)» y «Criterio o antibiograma (texto firmado)». Las columnas «Verificación», «Clase verificada», «Relación con la clase declarada», «Qué cambia en la extracción» y «Queda abierto» las derivó de ese texto el modelo de lenguaje (ingest_lectura_firmada.py), y su rótulo lo dice: «(lo codificó el modelo)».</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Sección 3.4. La columna «queda abierto» dice lo que la lectura no resolvió y no se cambió en la extracción.</t>
+          <t>Sección 3.4. «Queda abierto» dice lo que la lectura no resolvió y no se cambió en la extracción.</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>clase_en_la_extraccion_antes</t>
+          <t>Clase en la extracción, antes</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -588,7 +588,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>procedencia_antes</t>
+          <t>Procedencia de la clase, antes</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -600,7 +600,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>verificacion</t>
+          <t>Verificación (lo codificó el modelo)</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -612,7 +612,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>clase_verificada_codificada</t>
+          <t>Clase verificada (lo codificó el modelo)</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -624,7 +624,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>relacion_con_la_declarada</t>
+          <t>Relación con la clase declarada (lo codificó el modelo)</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -636,7 +636,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>cambia_en_la_extraccion</t>
+          <t>Qué cambia en la extracción (lo codificó el modelo)</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -648,7 +648,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>queda_abierto</t>
+          <t>Queda abierto (lo codificó el modelo)</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -660,7 +660,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>clase_verificada_firmada</t>
+          <t>Clase verificada (texto firmado)</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -672,7 +672,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>criterio_o_antibiograma_firmado</t>
+          <t>Criterio o antibiograma (texto firmado)</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -684,7 +684,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>firmado_por</t>
+          <t>Firmado por</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -755,52 +755,52 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>clase_en_la_extraccion_antes</t>
+          <t>Clase en la extracción, antes</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>procedencia_antes</t>
+          <t>Procedencia de la clase, antes</t>
         </is>
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>verificacion</t>
+          <t>Verificación (lo codificó el modelo)</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>clase_verificada_codificada</t>
+          <t>Clase verificada (lo codificó el modelo)</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>relacion_con_la_declarada</t>
+          <t>Relación con la clase declarada (lo codificó el modelo)</t>
         </is>
       </c>
       <c r="G1" s="9" t="inlineStr">
         <is>
-          <t>cambia_en_la_extraccion</t>
+          <t>Qué cambia en la extracción (lo codificó el modelo)</t>
         </is>
       </c>
       <c r="H1" s="9" t="inlineStr">
         <is>
-          <t>queda_abierto</t>
+          <t>Queda abierto (lo codificó el modelo)</t>
         </is>
       </c>
       <c r="I1" s="9" t="inlineStr">
         <is>
-          <t>clase_verificada_firmada</t>
+          <t>Clase verificada (texto firmado)</t>
         </is>
       </c>
       <c r="J1" s="9" t="inlineStr">
         <is>
-          <t>criterio_o_antibiograma_firmado</t>
+          <t>Criterio o antibiograma (texto firmado)</t>
         </is>
       </c>
       <c r="K1" s="9" t="inlineStr">
         <is>
-          <t>firmado_por</t>
+          <t>Firmado por</t>
         </is>
       </c>
       <c r="L1" s="9" t="inlineStr">

--- a/verificables revisión sistemática/S23_clase_de_resistencia_comprobada.xlsx
+++ b/verificables revisión sistemática/S23_clase_de_resistencia_comprobada.xlsx
@@ -715,7 +715,7 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-19</t>
+          <t>Generado el 2026-10-20</t>
         </is>
       </c>
     </row>
